--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Multicolinealidad/universo_analitico_vif.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Multicolinealidad/universo_analitico_vif.xlsx
@@ -504,11 +504,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.898</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -517,12 +517,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -541,20 +541,20 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31.915</v>
+        <v>36.388</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -563,12 +563,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -596,11 +596,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10.573</v>
+        <v>13.221</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -609,12 +609,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
     </row>
@@ -633,20 +633,20 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>36.048</v>
+        <v>82.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -655,12 +655,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -688,11 +688,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7.128</v>
+        <v>9.391</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -701,12 +701,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -734,11 +734,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.477</v>
+        <v>2.574</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -747,12 +747,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -780,11 +780,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.704</v>
+        <v>2.449</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -793,12 +793,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -826,25 +826,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5.779</v>
+        <v>4.188</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -872,11 +872,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.152</v>
+        <v>1.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -885,12 +885,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -918,11 +918,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.265</v>
+        <v>2.084</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -931,12 +931,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -964,25 +964,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11.557</v>
+        <v>2.114</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13.982</v>
+        <v>2.144</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1044,25 +1044,39 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1182.398</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1076,39 +1090,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1329.161</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -1124,10 +1136,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1136,25 +1148,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4.434</v>
+        <v>8.381</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -1170,39 +1182,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>37.091</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -1218,39 +1228,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3.619</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1266,39 +1274,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>42.952</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -1314,39 +1320,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>32.439</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Perfecta</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -1362,39 +1366,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3.032</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1410,39 +1412,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>7.181</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -1470,25 +1470,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>2354914.55</v>
-      </c>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>No Calculado</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>VIF no calculable por varianza nula de la variable.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Evaluar por separado debido a varianza nula; el VIF no es calculable.</t>
         </is>
       </c>
     </row>
@@ -1504,37 +1502,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Baja redundancia estructural.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4.372</v>
+        <v>6.742</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -1550,37 +1548,37 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.167</v>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>5.555</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -1608,11 +1606,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.027</v>
+        <v>1.028</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1621,12 +1619,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1642,23 +1640,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Baja redundancia estructural.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>22.078</v>
+        <v>22.148</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1667,12 +1665,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
         </is>
       </c>
     </row>
@@ -1688,37 +1686,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1.934</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1746,11 +1744,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.97</v>
+        <v>2.999</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1759,12 +1757,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1783,20 +1781,20 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>14.153</v>
+        <v>14.559</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1805,12 +1803,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
     </row>
@@ -1826,10 +1824,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1838,11 +1836,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10.296</v>
+        <v>10.278</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1851,12 +1849,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
         </is>
       </c>
     </row>
@@ -1872,10 +1870,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1884,11 +1882,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7.427</v>
+        <v>7.54</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1897,12 +1895,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
         </is>
       </c>
     </row>
@@ -1918,10 +1916,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1930,11 +1928,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.705</v>
+        <v>2.722</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1943,12 +1941,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -1964,10 +1962,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1976,11 +1974,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2.883</v>
+        <v>2.965</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1989,12 +1987,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -2010,10 +2008,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2022,11 +2020,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.619</v>
+        <v>1.645</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2035,12 +2033,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
@@ -2068,11 +2066,11 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.815</v>
+        <v>2.878</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2081,12 +2079,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
         </is>
       </c>
     </row>
